--- a/Testing Data/Study Plan/WUBM.xlsx
+++ b/Testing Data/Study Plan/WUBM.xlsx
@@ -1,28 +1,283 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\HKIT Course Management System V2\Testing Data\Study Plan\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B54A24-20B0-4A40-8B4B-0B053687F547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="83">
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>Intake Level</t>
+  </si>
+  <si>
+    <t>student ID</t>
+  </si>
+  <si>
+    <t>Intake term</t>
+  </si>
+  <si>
+    <t>study mode</t>
+  </si>
+  <si>
+    <t>programme stream</t>
+  </si>
+  <si>
+    <t>Module code</t>
+  </si>
+  <si>
+    <t>Study term</t>
+  </si>
+  <si>
+    <t>LEE HUNG</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>32554001</t>
+  </si>
+  <si>
+    <t>T2025B</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>nil</t>
+  </si>
+  <si>
+    <t>BS414</t>
+  </si>
+  <si>
+    <t>BS412</t>
+  </si>
+  <si>
+    <t>BS402</t>
+  </si>
+  <si>
+    <t>GE441</t>
+  </si>
+  <si>
+    <t>BUS699</t>
+  </si>
+  <si>
+    <t>T2025C</t>
+  </si>
+  <si>
+    <t>BUS693</t>
+  </si>
+  <si>
+    <t>BUS692</t>
+  </si>
+  <si>
+    <t>BUS698</t>
+  </si>
+  <si>
+    <t>T2026A</t>
+  </si>
+  <si>
+    <t>BUS6A1</t>
+  </si>
+  <si>
+    <t>LEE HONG YAT</t>
+  </si>
+  <si>
+    <t>32554002</t>
+  </si>
+  <si>
+    <t>HD405</t>
+  </si>
+  <si>
+    <t>HD404</t>
+  </si>
+  <si>
+    <t>LEE PO SHING</t>
+  </si>
+  <si>
+    <t>32554003</t>
+  </si>
+  <si>
+    <t>BS404</t>
+  </si>
+  <si>
+    <t>HD403</t>
+  </si>
+  <si>
+    <t>CHU HO LING</t>
+  </si>
+  <si>
+    <t>32554004</t>
+  </si>
+  <si>
+    <t>BS415</t>
+  </si>
+  <si>
+    <t>LAM HIU LOK</t>
+  </si>
+  <si>
+    <t>32554005</t>
+  </si>
+  <si>
+    <t>FUNG KIN FAAT</t>
+  </si>
+  <si>
+    <t>12554001</t>
+  </si>
+  <si>
+    <t>T2026C</t>
+  </si>
+  <si>
+    <t>LI HIU TIK SIMON</t>
+  </si>
+  <si>
+    <t>12554002</t>
+  </si>
+  <si>
+    <t>WONG KWOK IN</t>
+  </si>
+  <si>
+    <t>32454003</t>
+  </si>
+  <si>
+    <t>T2024B</t>
+  </si>
+  <si>
+    <t>BS413</t>
+  </si>
+  <si>
+    <t>T2025A</t>
+  </si>
+  <si>
+    <t>HO HO YAN</t>
+  </si>
+  <si>
+    <t>32554006</t>
+  </si>
+  <si>
+    <t>TANG KWAN NGAI</t>
+  </si>
+  <si>
+    <t>12554003</t>
+  </si>
+  <si>
+    <t>TONG KWOK SHAN</t>
+  </si>
+  <si>
+    <t>12554004</t>
+  </si>
+  <si>
+    <t>HD404_N</t>
+  </si>
+  <si>
+    <t>LUI YEE LING</t>
+  </si>
+  <si>
+    <t>22460033</t>
+  </si>
+  <si>
+    <t>YIP WING FAI</t>
+  </si>
+  <si>
+    <t>22654001</t>
+  </si>
+  <si>
+    <t>CHAN KWUN FONG</t>
+  </si>
+  <si>
+    <t>22654002</t>
+  </si>
+  <si>
+    <t>NG CHUNG WAI</t>
+  </si>
+  <si>
+    <t>22654003</t>
+  </si>
+  <si>
+    <t>T2026B</t>
+  </si>
+  <si>
+    <t>WONG LOK YI</t>
+  </si>
+  <si>
+    <t>22654404</t>
+  </si>
+  <si>
+    <t>LAU JESSIE SIN KWAN</t>
+  </si>
+  <si>
+    <t>22654005</t>
+  </si>
+  <si>
+    <t>JOR WAI YIN</t>
+  </si>
+  <si>
+    <t>22654006</t>
+  </si>
+  <si>
+    <t>GS402</t>
+  </si>
+  <si>
+    <t>GS401</t>
+  </si>
+  <si>
+    <t>FUNG YEE MAN</t>
+  </si>
+  <si>
+    <t>22654007</t>
+  </si>
+  <si>
+    <t>BS406</t>
+  </si>
+  <si>
+    <t>WONG HUNG KWONG</t>
+  </si>
+  <si>
+    <t>32654001</t>
+  </si>
+  <si>
+    <t>MAK LOK MAN</t>
+  </si>
+  <si>
+    <t>32654002</t>
+  </si>
+  <si>
+    <t>GS413</t>
+  </si>
+  <si>
+    <t>LAW CHEUK YIN</t>
+  </si>
+  <si>
+    <t>32654003</t>
+  </si>
+  <si>
+    <t>FT</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,7 +311,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -79,44 +334,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -146,12 +401,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -190,150 +445,2053 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>6</v>
+      </c>
+      <c r="X1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" t="s">
+        <v>23</v>
+      </c>
+      <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" t="s">
+        <v>21</v>
+      </c>
+      <c r="T4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" t="s">
+        <v>21</v>
+      </c>
+      <c r="V5" t="s">
+        <v>23</v>
+      </c>
+      <c r="W5" t="s">
+        <v>12</v>
+      </c>
+      <c r="X5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>24</v>
+      </c>
+      <c r="T6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" t="s">
+        <v>21</v>
+      </c>
+      <c r="V6" t="s">
+        <v>23</v>
+      </c>
+      <c r="W6" t="s">
+        <v>12</v>
+      </c>
+      <c r="X6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>21</v>
+      </c>
+      <c r="T7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
+        <v>12</v>
+      </c>
+      <c r="V7" t="s">
+        <v>12</v>
+      </c>
+      <c r="W7" t="s">
+        <v>12</v>
+      </c>
+      <c r="X7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" t="s">
+        <v>21</v>
+      </c>
+      <c r="T8" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" t="s">
+        <v>12</v>
+      </c>
+      <c r="V8" t="s">
+        <v>12</v>
+      </c>
+      <c r="W8" t="s">
+        <v>12</v>
+      </c>
+      <c r="X8" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" t="s">
+        <v>47</v>
+      </c>
+      <c r="S9" t="s">
+        <v>21</v>
+      </c>
+      <c r="T9" t="s">
+        <v>47</v>
+      </c>
+      <c r="U9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V9" t="s">
+        <v>12</v>
+      </c>
+      <c r="W9" t="s">
+        <v>12</v>
+      </c>
+      <c r="X9" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" t="s">
+        <v>21</v>
+      </c>
+      <c r="T10" t="s">
+        <v>23</v>
+      </c>
+      <c r="U10" t="s">
+        <v>12</v>
+      </c>
+      <c r="V10" t="s">
+        <v>12</v>
+      </c>
+      <c r="W10" t="s">
+        <v>12</v>
+      </c>
+      <c r="X10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R11" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U11" t="s">
+        <v>12</v>
+      </c>
+      <c r="V11" t="s">
+        <v>12</v>
+      </c>
+      <c r="W11" t="s">
+        <v>12</v>
+      </c>
+      <c r="X11" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S12" t="s">
+        <v>24</v>
+      </c>
+      <c r="T12" t="s">
+        <v>23</v>
+      </c>
+      <c r="U12" t="s">
+        <v>21</v>
+      </c>
+      <c r="V12" t="s">
+        <v>23</v>
+      </c>
+      <c r="W12" t="s">
+        <v>12</v>
+      </c>
+      <c r="X12" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U13" t="s">
+        <v>12</v>
+      </c>
+      <c r="V13" t="s">
+        <v>12</v>
+      </c>
+      <c r="W13" t="s">
+        <v>12</v>
+      </c>
+      <c r="X13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
+        <v>40</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" t="s">
+        <v>12</v>
+      </c>
+      <c r="T14" t="s">
+        <v>12</v>
+      </c>
+      <c r="U14" t="s">
+        <v>12</v>
+      </c>
+      <c r="V14" t="s">
+        <v>12</v>
+      </c>
+      <c r="W14" t="s">
+        <v>12</v>
+      </c>
+      <c r="X14" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
+        <v>40</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" t="s">
+        <v>12</v>
+      </c>
+      <c r="T15" t="s">
+        <v>12</v>
+      </c>
+      <c r="U15" t="s">
+        <v>12</v>
+      </c>
+      <c r="V15" t="s">
+        <v>12</v>
+      </c>
+      <c r="W15" t="s">
+        <v>12</v>
+      </c>
+      <c r="X15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" t="s">
+        <v>12</v>
+      </c>
+      <c r="O16" t="s">
+        <v>12</v>
+      </c>
+      <c r="P16" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>12</v>
+      </c>
+      <c r="R16" t="s">
+        <v>12</v>
+      </c>
+      <c r="S16" t="s">
+        <v>12</v>
+      </c>
+      <c r="T16" t="s">
+        <v>12</v>
+      </c>
+      <c r="U16" t="s">
+        <v>12</v>
+      </c>
+      <c r="V16" t="s">
+        <v>12</v>
+      </c>
+      <c r="W16" t="s">
+        <v>12</v>
+      </c>
+      <c r="X16" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" t="s">
+        <v>12</v>
+      </c>
+      <c r="O17" t="s">
+        <v>12</v>
+      </c>
+      <c r="P17" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>12</v>
+      </c>
+      <c r="R17" t="s">
+        <v>12</v>
+      </c>
+      <c r="S17" t="s">
+        <v>12</v>
+      </c>
+      <c r="T17" t="s">
+        <v>12</v>
+      </c>
+      <c r="U17" t="s">
+        <v>12</v>
+      </c>
+      <c r="V17" t="s">
+        <v>12</v>
+      </c>
+      <c r="W17" t="s">
+        <v>12</v>
+      </c>
+      <c r="X17" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" t="s">
+        <v>12</v>
+      </c>
+      <c r="N18" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" t="s">
+        <v>12</v>
+      </c>
+      <c r="P18" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>12</v>
+      </c>
+      <c r="R18" t="s">
+        <v>12</v>
+      </c>
+      <c r="S18" t="s">
+        <v>12</v>
+      </c>
+      <c r="T18" t="s">
+        <v>12</v>
+      </c>
+      <c r="U18" t="s">
+        <v>12</v>
+      </c>
+      <c r="V18" t="s">
+        <v>12</v>
+      </c>
+      <c r="W18" t="s">
+        <v>12</v>
+      </c>
+      <c r="X18" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" t="s">
+        <v>71</v>
+      </c>
+      <c r="L19" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O19" t="s">
+        <v>12</v>
+      </c>
+      <c r="P19" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>12</v>
+      </c>
+      <c r="R19" t="s">
+        <v>12</v>
+      </c>
+      <c r="S19" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" t="s">
+        <v>12</v>
+      </c>
+      <c r="U19" t="s">
+        <v>12</v>
+      </c>
+      <c r="V19" t="s">
+        <v>12</v>
+      </c>
+      <c r="W19" t="s">
+        <v>12</v>
+      </c>
+      <c r="X19" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" t="s">
+        <v>12</v>
+      </c>
+      <c r="N20" t="s">
+        <v>12</v>
+      </c>
+      <c r="O20" t="s">
+        <v>12</v>
+      </c>
+      <c r="P20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>12</v>
+      </c>
+      <c r="R20" t="s">
+        <v>12</v>
+      </c>
+      <c r="S20" t="s">
+        <v>12</v>
+      </c>
+      <c r="T20" t="s">
+        <v>12</v>
+      </c>
+      <c r="U20" t="s">
+        <v>12</v>
+      </c>
+      <c r="V20" t="s">
+        <v>12</v>
+      </c>
+      <c r="W20" t="s">
+        <v>12</v>
+      </c>
+      <c r="X20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L21" t="s">
+        <v>12</v>
+      </c>
+      <c r="M21" t="s">
+        <v>12</v>
+      </c>
+      <c r="N21" t="s">
+        <v>12</v>
+      </c>
+      <c r="O21" t="s">
+        <v>12</v>
+      </c>
+      <c r="P21" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>12</v>
+      </c>
+      <c r="R21" t="s">
+        <v>12</v>
+      </c>
+      <c r="S21" t="s">
+        <v>12</v>
+      </c>
+      <c r="T21" t="s">
+        <v>12</v>
+      </c>
+      <c r="U21" t="s">
+        <v>12</v>
+      </c>
+      <c r="V21" t="s">
+        <v>12</v>
+      </c>
+      <c r="W21" t="s">
+        <v>12</v>
+      </c>
+      <c r="X21" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" t="s">
+        <v>12</v>
+      </c>
+      <c r="N22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R22" t="s">
+        <v>12</v>
+      </c>
+      <c r="S22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T22" t="s">
+        <v>12</v>
+      </c>
+      <c r="U22" t="s">
+        <v>12</v>
+      </c>
+      <c r="V22" t="s">
+        <v>12</v>
+      </c>
+      <c r="W22" t="s">
+        <v>12</v>
+      </c>
+      <c r="X22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s">
+        <v>63</v>
+      </c>
+      <c r="I23" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" t="s">
+        <v>12</v>
+      </c>
+      <c r="K23" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" t="s">
+        <v>12</v>
+      </c>
+      <c r="N23" t="s">
+        <v>12</v>
+      </c>
+      <c r="O23" t="s">
+        <v>12</v>
+      </c>
+      <c r="P23" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>12</v>
+      </c>
+      <c r="R23" t="s">
+        <v>12</v>
+      </c>
+      <c r="S23" t="s">
+        <v>12</v>
+      </c>
+      <c r="T23" t="s">
+        <v>12</v>
+      </c>
+      <c r="U23" t="s">
+        <v>12</v>
+      </c>
+      <c r="V23" t="s">
+        <v>12</v>
+      </c>
+      <c r="W23" t="s">
+        <v>12</v>
+      </c>
+      <c r="X23" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Z1 A3:D23 A2:D2 F2:Z2 F3:Z23" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>